--- a/data/trans_orig/DC-Clase-trans_orig.xlsx
+++ b/data/trans_orig/DC-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2007</t>
+          <t>Población con dolor crónico en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>61578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>93852</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51469</t>
+          <t>51587</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80331</t>
+          <t>80514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119293</t>
+          <t>118948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>162346</t>
+          <t>162888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382820</t>
+          <t>379924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413515</t>
+          <t>412198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226349</t>
+          <t>226166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255211</t>
+          <t>255093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>618111</t>
+          <t>617569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>661164</t>
+          <t>661509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30452</t>
+          <t>31147</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56789</t>
+          <t>55602</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93929</t>
+          <t>92570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128139</t>
+          <t>126792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131710</t>
+          <t>129592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175932</t>
+          <t>174723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310145</t>
+          <t>311332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>336482</t>
+          <t>335787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243726</t>
+          <t>245073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277936</t>
+          <t>279295</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>562867</t>
+          <t>564076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>607089</t>
+          <t>609207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91824</t>
+          <t>92958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129425</t>
+          <t>130334</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63053</t>
+          <t>63917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138345</t>
+          <t>138933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185764</t>
+          <t>184369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412964</t>
+          <t>412055</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450565</t>
+          <t>449431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104729</t>
+          <t>103865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127508</t>
+          <t>128053</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>524407</t>
+          <t>525802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>571826</t>
+          <t>571238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>238466</t>
+          <t>238841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>299506</t>
+          <t>300914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190956</t>
+          <t>190898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238746</t>
+          <t>240254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>445729</t>
+          <t>444895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>525231</t>
+          <t>519844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>938828</t>
+          <t>937420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>999868</t>
+          <t>999493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>475539</t>
+          <t>474031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>523329</t>
+          <t>523387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1427389</t>
+          <t>1432776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1506891</t>
+          <t>1507725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>57198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87862</t>
+          <t>87665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137513</t>
+          <t>135652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181861</t>
+          <t>178449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>203344</t>
+          <t>203891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>257272</t>
+          <t>256639</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>262693</t>
+          <t>262890</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293273</t>
+          <t>293357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386891</t>
+          <t>390303</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>431239</t>
+          <t>433100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>662035</t>
+          <t>662668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>715963</t>
+          <t>715416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>315473</t>
+          <t>312903</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>377841</t>
+          <t>374408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>318962</t>
+          <t>319296</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>381545</t>
+          <t>385366</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284847</t>
+          <t>284484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295300</t>
+          <t>295306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>870919</t>
+          <t>874352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>933287</t>
+          <t>935857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1165415</t>
+          <t>1161594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1227998</t>
+          <t>1227664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>530255</t>
+          <t>534369</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>619456</t>
+          <t>620513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>890873</t>
+          <t>891815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>998230</t>
+          <t>991245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1450634</t>
+          <t>1443649</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1585790</t>
+          <t>1581040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2650734</t>
+          <t>2649677</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2739935</t>
+          <t>2735821</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2379894</t>
+          <t>2386879</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2487251</t>
+          <t>2486309</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5062524</t>
+          <t>5067274</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5197680</t>
+          <t>5204665</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2012</t>
+          <t>Población con dolor crónico en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46880</t>
+          <t>46692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46590</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77242</t>
+          <t>77133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113943</t>
+          <t>116535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390331</t>
+          <t>390519</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412886</t>
+          <t>413396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238674</t>
+          <t>237694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267864</t>
+          <t>266335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>637722</t>
+          <t>635130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>674423</t>
+          <t>674532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27654</t>
+          <t>27735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53636</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51419</t>
+          <t>50712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>80009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85477</t>
+          <t>85398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125160</t>
+          <t>124774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365161</t>
+          <t>365871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391143</t>
+          <t>391062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256228</t>
+          <t>258002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>286592</t>
+          <t>287299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>631648</t>
+          <t>632034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>671331</t>
+          <t>671410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57571</t>
+          <t>57534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91657</t>
+          <t>91173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46590</t>
+          <t>46076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73203</t>
+          <t>72910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111694</t>
+          <t>112694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157465</t>
+          <t>156987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537758</t>
+          <t>538242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>571844</t>
+          <t>571881</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186926</t>
+          <t>187219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>213539</t>
+          <t>214053</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>732079</t>
+          <t>732557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>777850</t>
+          <t>776850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128925</t>
+          <t>128101</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>173394</t>
+          <t>174871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144617</t>
+          <t>145520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191639</t>
+          <t>191380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284501</t>
+          <t>285536</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353485</t>
+          <t>352208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>985615</t>
+          <t>984138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1030084</t>
+          <t>1030908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575018</t>
+          <t>575277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>622040</t>
+          <t>621137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1572182</t>
+          <t>1573459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1641166</t>
+          <t>1640131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36974</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63281</t>
+          <t>65100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185376</t>
+          <t>189109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>237108</t>
+          <t>241209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230036</t>
+          <t>233991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291635</t>
+          <t>288321</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447315</t>
+          <t>445496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473622</t>
+          <t>473697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>524414</t>
+          <t>520313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>576146</t>
+          <t>572413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>980483</t>
+          <t>983797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1042082</t>
+          <t>1038127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254721</t>
+          <t>253660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>313109</t>
+          <t>311641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261276</t>
+          <t>257159</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>324523</t>
+          <t>320816</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250626</t>
+          <t>249110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262899</t>
+          <t>262913</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>796242</t>
+          <t>797710</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>854630</t>
+          <t>855691</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1051710</t>
+          <t>1055417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1114957</t>
+          <t>1119074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>316414</t>
+          <t>318916</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>392970</t>
+          <t>393120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>792204</t>
+          <t>793031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>900252</t>
+          <t>896331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1133862</t>
+          <t>1140015</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1263203</t>
+          <t>1263448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3028940</t>
+          <t>3028790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3105496</t>
+          <t>3102994</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2649873</t>
+          <t>2653794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2757921</t>
+          <t>2757094</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5708832</t>
+          <t>5708587</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5838173</t>
+          <t>5832020</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2016</t>
+          <t>Población con dolor crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>34518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60277</t>
+          <t>60969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>56103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70227</t>
+          <t>71179</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107624</t>
+          <t>107149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368815</t>
+          <t>368123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396439</t>
+          <t>394574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290322</t>
+          <t>290952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316262</t>
+          <t>316774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668523</t>
+          <t>668998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>705920</t>
+          <t>704968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>34326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50372</t>
+          <t>51079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81409</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69855</t>
+          <t>69402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104929</t>
+          <t>105139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342787</t>
+          <t>342901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363198</t>
+          <t>363439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290864</t>
+          <t>293426</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321901</t>
+          <t>321194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>644571</t>
+          <t>644361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>679645</t>
+          <t>680098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60755</t>
+          <t>61505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30560</t>
+          <t>31273</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71679</t>
+          <t>70953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106327</t>
+          <t>107146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461159</t>
+          <t>460409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113334</t>
+          <t>112630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135563</t>
+          <t>134850</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>581709</t>
+          <t>580890</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>616357</t>
+          <t>617083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98448</t>
+          <t>100371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143777</t>
+          <t>140336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120242</t>
+          <t>119950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165650</t>
+          <t>166219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233608</t>
+          <t>229687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295025</t>
+          <t>293642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1005861</t>
+          <t>1009302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1051190</t>
+          <t>1049267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>660226</t>
+          <t>659657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705634</t>
+          <t>705926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1680489</t>
+          <t>1681872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1741906</t>
+          <t>1745827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66263</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99237</t>
+          <t>102106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>147763</t>
+          <t>145339</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>193312</t>
+          <t>192694</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225569</t>
+          <t>224579</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284603</t>
+          <t>282438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>521469</t>
+          <t>518600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>554443</t>
+          <t>553310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>544932</t>
+          <t>545550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>590481</t>
+          <t>592905</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1074347</t>
+          <t>1076512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1133381</t>
+          <t>1134371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>165098</t>
+          <t>165172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>217387</t>
+          <t>216227</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166571</t>
+          <t>166978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222857</t>
+          <t>222649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278480</t>
+          <t>278788</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286182</t>
+          <t>287145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>864638</t>
+          <t>865798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>916927</t>
+          <t>916853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1146313</t>
+          <t>1146521</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1202599</t>
+          <t>1202192</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>290451</t>
+          <t>289043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>357440</t>
+          <t>359668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>601868</t>
+          <t>600575</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>696035</t>
+          <t>698324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>911118</t>
+          <t>902913</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1033257</t>
+          <t>1026419</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3028282</t>
+          <t>3026054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3095271</t>
+          <t>3096679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2835561</t>
+          <t>2833272</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2929728</t>
+          <t>2931021</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5884061</t>
+          <t>5890899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6006200</t>
+          <t>6014405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2023</t>
+          <t>Población con dolor crónico en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74562</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110142</t>
+          <t>108461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136992</t>
+          <t>136668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171972</t>
+          <t>170052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219282</t>
+          <t>219073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>270529</t>
+          <t>270264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395070</t>
+          <t>396751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>430650</t>
+          <t>429917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275495</t>
+          <t>277415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310475</t>
+          <t>310799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682150</t>
+          <t>682415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>733397</t>
+          <t>733606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71681</t>
+          <t>72740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105642</t>
+          <t>104285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>121574</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152292</t>
+          <t>152302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198961</t>
+          <t>199072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248093</t>
+          <t>247617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346571</t>
+          <t>347928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>380532</t>
+          <t>379473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230288</t>
+          <t>230278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>263580</t>
+          <t>261006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>586700</t>
+          <t>587176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>635832</t>
+          <t>635721</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>42623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175630</t>
+          <t>175203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65042</t>
+          <t>65065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85047</t>
+          <t>84373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77994</t>
+          <t>84091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>263516</t>
+          <t>260154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492634</t>
+          <t>493061</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632018</t>
+          <t>625641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81864</t>
+          <t>82538</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101869</t>
+          <t>101846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>571659</t>
+          <t>575021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>757181</t>
+          <t>751084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223796</t>
+          <t>225304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>279249</t>
+          <t>282037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>342823</t>
+          <t>342335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>723744</t>
+          <t>683907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>577888</t>
+          <t>576930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1088639</t>
+          <t>1154205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>57,34%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>755570</t>
+          <t>752782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>811023</t>
+          <t>809515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>254350</t>
+          <t>294187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635271</t>
+          <t>635759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>924273</t>
+          <t>858707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1435024</t>
+          <t>1435982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101526</t>
+          <t>102157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139229</t>
+          <t>140666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>361689</t>
+          <t>362370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>526805</t>
+          <t>526461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>473011</t>
+          <t>472830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>668517</t>
+          <t>662499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335817</t>
+          <t>334380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>373520</t>
+          <t>372889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314530</t>
+          <t>314874</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>479646</t>
+          <t>478965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>647864</t>
+          <t>653882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>843370</t>
+          <t>843551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45985</t>
+          <t>45843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>253652</t>
+          <t>254408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>302059</t>
+          <t>300214</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>274754</t>
+          <t>273471</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>332495</t>
+          <t>335039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194522</t>
+          <t>194664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226168</t>
+          <t>227170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>459312</t>
+          <t>461157</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>507719</t>
+          <t>506963</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>669383</t>
+          <t>666839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>727124</t>
+          <t>728407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>536315</t>
+          <t>536201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>749654</t>
+          <t>749068</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1385146</t>
+          <t>1373081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1980594</t>
+          <t>1886540</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1982642</t>
+          <t>1990378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2743669</t>
+          <t>2682017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2626406</t>
+          <t>2626992</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2839745</t>
+          <t>2839859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1597164</t>
+          <t>1691218</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2192612</t>
+          <t>2204677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4210149</t>
+          <t>4271801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4971176</t>
+          <t>4963440</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DC-Clase-trans_orig.xlsx
+++ b/data/trans_orig/DC-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61578</t>
+          <t>61279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93852</t>
+          <t>92236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51587</t>
+          <t>51759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80514</t>
+          <t>79874</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118948</t>
+          <t>121000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>162888</t>
+          <t>165528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379924</t>
+          <t>381540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412198</t>
+          <t>412497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226166</t>
+          <t>226806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255093</t>
+          <t>254921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>617569</t>
+          <t>614929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>661509</t>
+          <t>659457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55602</t>
+          <t>54553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92570</t>
+          <t>92160</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126792</t>
+          <t>126618</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129592</t>
+          <t>131602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174723</t>
+          <t>173706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311332</t>
+          <t>312381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335787</t>
+          <t>336247</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>245073</t>
+          <t>245247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>279295</t>
+          <t>279705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>564076</t>
+          <t>565093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>609207</t>
+          <t>607197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92958</t>
+          <t>91901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130334</t>
+          <t>129625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63917</t>
+          <t>63812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138933</t>
+          <t>141342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184369</t>
+          <t>185602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412055</t>
+          <t>412764</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449431</t>
+          <t>450488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103865</t>
+          <t>103970</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128053</t>
+          <t>129063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525802</t>
+          <t>524569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>571238</t>
+          <t>568829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>238841</t>
+          <t>240989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>300914</t>
+          <t>298855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190898</t>
+          <t>191338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240254</t>
+          <t>237446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>444895</t>
+          <t>444748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>519844</t>
+          <t>520308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>937420</t>
+          <t>939479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>999493</t>
+          <t>997345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>474031</t>
+          <t>476839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>523387</t>
+          <t>522947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1432776</t>
+          <t>1432312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1507725</t>
+          <t>1507872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57198</t>
+          <t>56877</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87665</t>
+          <t>85484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135652</t>
+          <t>136482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>178449</t>
+          <t>180467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>203891</t>
+          <t>203237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256639</t>
+          <t>256155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>262890</t>
+          <t>265071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293357</t>
+          <t>293678</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>390303</t>
+          <t>388285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>433100</t>
+          <t>432270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>662668</t>
+          <t>663152</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>715416</t>
+          <t>716070</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>312903</t>
+          <t>312963</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>374408</t>
+          <t>374397</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>319296</t>
+          <t>318837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>385366</t>
+          <t>381463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284484</t>
+          <t>284654</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295306</t>
+          <t>295207</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>874352</t>
+          <t>874363</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>935857</t>
+          <t>935797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1161594</t>
+          <t>1165497</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1227664</t>
+          <t>1228123</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>534369</t>
+          <t>527510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>620513</t>
+          <t>619339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>891815</t>
+          <t>893927</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>991245</t>
+          <t>997024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1443649</t>
+          <t>1450171</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1581040</t>
+          <t>1581970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2649677</t>
+          <t>2650851</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2735821</t>
+          <t>2742680</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2386879</t>
+          <t>2381100</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2486309</t>
+          <t>2484197</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5067274</t>
+          <t>5066344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5204665</t>
+          <t>5198143</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46692</t>
+          <t>46863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>47661</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76760</t>
+          <t>78611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77133</t>
+          <t>77194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116535</t>
+          <t>113865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390519</t>
+          <t>390348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413396</t>
+          <t>413013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237694</t>
+          <t>235843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266335</t>
+          <t>266793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>635130</t>
+          <t>637800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>674532</t>
+          <t>674471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27735</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52926</t>
+          <t>53690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50712</t>
+          <t>50021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80009</t>
+          <t>80645</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85398</t>
+          <t>85005</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124774</t>
+          <t>126114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365871</t>
+          <t>365107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391062</t>
+          <t>391178</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>258002</t>
+          <t>257366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287299</t>
+          <t>287990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>632034</t>
+          <t>630694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>671410</t>
+          <t>671803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57534</t>
+          <t>58077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91173</t>
+          <t>90767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46076</t>
+          <t>44680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72910</t>
+          <t>73367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112694</t>
+          <t>109833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156987</t>
+          <t>154936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538242</t>
+          <t>538648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>571881</t>
+          <t>571338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187219</t>
+          <t>186762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>214053</t>
+          <t>215449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>732557</t>
+          <t>734608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>776850</t>
+          <t>779711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128101</t>
+          <t>129108</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174871</t>
+          <t>176667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>144763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191380</t>
+          <t>194963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>285536</t>
+          <t>283673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>352208</t>
+          <t>354321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>984138</t>
+          <t>982342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1030908</t>
+          <t>1029901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575277</t>
+          <t>571694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>621137</t>
+          <t>621894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1573459</t>
+          <t>1571346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1640131</t>
+          <t>1641994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65100</t>
+          <t>63937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>189109</t>
+          <t>185636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>241209</t>
+          <t>236039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233991</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288321</t>
+          <t>289135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>445496</t>
+          <t>446659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473697</t>
+          <t>474206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520313</t>
+          <t>525483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>572413</t>
+          <t>575886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>983797</t>
+          <t>982983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1038127</t>
+          <t>1040802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>253660</t>
+          <t>255549</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>311641</t>
+          <t>316730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>257159</t>
+          <t>260368</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320816</t>
+          <t>321941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249110</t>
+          <t>249187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262913</t>
+          <t>263146</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>797710</t>
+          <t>792621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>855691</t>
+          <t>853802</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1055417</t>
+          <t>1054292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1119074</t>
+          <t>1115865</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>318916</t>
+          <t>319354</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>393120</t>
+          <t>390932</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>793031</t>
+          <t>794293</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>896331</t>
+          <t>898286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1140015</t>
+          <t>1137017</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1263448</t>
+          <t>1264100</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3028790</t>
+          <t>3030978</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3102994</t>
+          <t>3102556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2653794</t>
+          <t>2651839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2757094</t>
+          <t>2755832</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5708587</t>
+          <t>5707935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5832020</t>
+          <t>5835018</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34518</t>
+          <t>33354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60969</t>
+          <t>60038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56103</t>
+          <t>55492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71179</t>
+          <t>71254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107149</t>
+          <t>106911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368123</t>
+          <t>369054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394574</t>
+          <t>395738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290952</t>
+          <t>291563</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316774</t>
+          <t>316328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668998</t>
+          <t>669236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704968</t>
+          <t>704893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34326</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51079</t>
+          <t>49876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>79606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69402</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105139</t>
+          <t>105158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>343616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363439</t>
+          <t>362778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>293426</t>
+          <t>292667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321194</t>
+          <t>322397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>644361</t>
+          <t>644342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680098</t>
+          <t>680226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34493</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61505</t>
+          <t>61106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31273</t>
+          <t>30350</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>52802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70953</t>
+          <t>70086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107146</t>
+          <t>107275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460409</t>
+          <t>460808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487421</t>
+          <t>487191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112630</t>
+          <t>113321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134850</t>
+          <t>135773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580890</t>
+          <t>580761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>617083</t>
+          <t>617950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100371</t>
+          <t>100991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140336</t>
+          <t>142836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119950</t>
+          <t>119711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166219</t>
+          <t>164262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229687</t>
+          <t>233773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293642</t>
+          <t>297990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1009302</t>
+          <t>1006802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1049267</t>
+          <t>1048647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>659657</t>
+          <t>661614</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705926</t>
+          <t>706165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1681872</t>
+          <t>1677524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1745827</t>
+          <t>1741741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>66688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102106</t>
+          <t>101176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>145339</t>
+          <t>145738</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192694</t>
+          <t>194173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224579</t>
+          <t>225513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282438</t>
+          <t>285027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>518600</t>
+          <t>519530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>553310</t>
+          <t>554018</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>545550</t>
+          <t>544071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>592905</t>
+          <t>592506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1076512</t>
+          <t>1073923</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1134371</t>
+          <t>1133437</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>165172</t>
+          <t>164610</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>216227</t>
+          <t>215067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166978</t>
+          <t>166739</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222649</t>
+          <t>220028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278788</t>
+          <t>278399</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>286174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>865798</t>
+          <t>866958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>916853</t>
+          <t>917415</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1146521</t>
+          <t>1149142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1202192</t>
+          <t>1202431</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>289043</t>
+          <t>289884</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>359668</t>
+          <t>360242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>600575</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>698324</t>
+          <t>697584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>902913</t>
+          <t>911177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1026419</t>
+          <t>1028242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3026054</t>
+          <t>3025480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3096679</t>
+          <t>3095838</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2833272</t>
+          <t>2834012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2931021</t>
+          <t>2931012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5890899</t>
+          <t>5889076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6014405</t>
+          <t>6006141</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90699</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75295</t>
+          <t>82489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108461</t>
+          <t>118618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>153706</t>
+          <t>169222</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136668</t>
+          <t>151668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170052</t>
+          <t>188909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>244405</t>
+          <t>268909</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219073</t>
+          <t>245201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>270264</t>
+          <t>296396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>414513</t>
+          <t>450931</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396751</t>
+          <t>432000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429917</t>
+          <t>468129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>293761</t>
+          <t>319189</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277415</t>
+          <t>299502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310799</t>
+          <t>336743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>708274</t>
+          <t>770120</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682415</t>
+          <t>742633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>733606</t>
+          <t>793828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87724</t>
+          <t>92354</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72740</t>
+          <t>76272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104285</t>
+          <t>109802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135659</t>
+          <t>154226</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121574</t>
+          <t>137804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>172919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>223383</t>
+          <t>246581</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199072</t>
+          <t>222427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>247617</t>
+          <t>275521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>364489</t>
+          <t>390858</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347928</t>
+          <t>373410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>379473</t>
+          <t>406940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>246921</t>
+          <t>268917</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230278</t>
+          <t>250224</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>261006</t>
+          <t>285339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>611410</t>
+          <t>659774</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>587176</t>
+          <t>630834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>635721</t>
+          <t>683928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>105808</t>
+          <t>116541</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>98179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175203</t>
+          <t>135669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74891</t>
+          <t>84731</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>74461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84373</t>
+          <t>95877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>180698</t>
+          <t>201273</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84091</t>
+          <t>179047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260154</t>
+          <t>224593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>562456</t>
+          <t>355071</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493061</t>
+          <t>335943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625641</t>
+          <t>373433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92020</t>
+          <t>102766</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82538</t>
+          <t>91620</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101846</t>
+          <t>113036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>654477</t>
+          <t>457836</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575021</t>
+          <t>434516</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>751084</t>
+          <t>480062</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>250248</t>
+          <t>267283</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>225304</t>
+          <t>241476</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282037</t>
+          <t>300195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>484564</t>
+          <t>316060</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>342335</t>
+          <t>292421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>683907</t>
+          <t>340678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>734812</t>
+          <t>583344</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>576930</t>
+          <t>545877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1154205</t>
+          <t>620532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>784571</t>
+          <t>864560</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>752782</t>
+          <t>831648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>809515</t>
+          <t>890367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>493530</t>
+          <t>545151</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294187</t>
+          <t>520533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635759</t>
+          <t>568790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1278100</t>
+          <t>1409710</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>858707</t>
+          <t>1372522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1435982</t>
+          <t>1447177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>119551</t>
+          <t>135801</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102157</t>
+          <t>116171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140666</t>
+          <t>160021</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,22 +10040,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>414083</t>
+          <t>380670</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>362370</t>
+          <t>357853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>526461</t>
+          <t>404924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>533634</t>
+          <t>516471</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>472830</t>
+          <t>485254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>662499</t>
+          <t>552407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>355495</t>
+          <t>432163</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334380</t>
+          <t>407943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372889</t>
+          <t>451793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,27 +10153,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>427252</t>
+          <t>450180</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314874</t>
+          <t>425926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>478965</t>
+          <t>472997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>782747</t>
+          <t>882343</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>653882</t>
+          <t>846407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>843551</t>
+          <t>913560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25989</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45843</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>277804</t>
+          <t>304284</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254408</t>
+          <t>280861</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>300214</t>
+          <t>332056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>303793</t>
+          <t>329977</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>273471</t>
+          <t>297752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>335039</t>
+          <t>361242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>214518</t>
+          <t>211535</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194664</t>
+          <t>193930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227170</t>
+          <t>222194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>483567</t>
+          <t>539997</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>461157</t>
+          <t>512225</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>506963</t>
+          <t>563420</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>698085</t>
+          <t>751532</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>666839</t>
+          <t>720267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>728407</t>
+          <t>783757</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>680020</t>
+          <t>737360</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>536201</t>
+          <t>690030</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>749068</t>
+          <t>793642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1540706</t>
+          <t>1409194</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1373081</t>
+          <t>1357371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1886540</t>
+          <t>1457286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2220726</t>
+          <t>2146554</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1990378</t>
+          <t>2071994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2682017</t>
+          <t>2215240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2696040</t>
+          <t>2705116</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2626992</t>
+          <t>2648834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2839859</t>
+          <t>2752446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2037052</t>
+          <t>2226199</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1691218</t>
+          <t>2178107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2204677</t>
+          <t>2278022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4733092</t>
+          <t>4931315</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4271801</t>
+          <t>4862629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4963440</t>
+          <t>5005875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
